--- a/DailyOpsConfig.xlsx
+++ b/DailyOpsConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwalczuk\Desktop\DailyOps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwalczuk\Desktop\DailyOps-RawStarts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF2DCCA-351D-4413-A8E9-D24B18ED93E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_DBD547B210A6F92AF99F2452D5041114510B7B0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
   <si>
     <t>Code</t>
   </si>
@@ -50,6 +50,9 @@
     <t>FileWords</t>
   </si>
   <si>
+    <t>Areas</t>
+  </si>
+  <si>
     <t>HMS</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>SMS,LMS,FEL</t>
   </si>
   <si>
+    <t>LMS,SMS</t>
+  </si>
+  <si>
     <t>FEL</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
     <t>ReportFolder</t>
   </si>
   <si>
+    <t>J:\Departments\Machine\4M\KACPER\DAILY OPS REPORTING</t>
+  </si>
+  <si>
     <t>Where the Daily Ops Report workbook is (newest .xlsm there is offered first).</t>
   </si>
   <si>
@@ -113,7 +122,7 @@
     <t>J:\Departments\Machine\4M</t>
   </si>
   <si>
-    <t>Where the machine start-time trackers are.</t>
+    <t>Where the machine start-time trackers are (they fill in machines the raw data has nothing for).</t>
   </si>
   <si>
     <t>ScheduleFolder</t>
@@ -176,24 +185,27 @@
     <t>SaveOverOriginal</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes = save the report workbook in place (a backup is kept). No = save a copy in the output folder (default here, so this test version doesn't touch the real report).</t>
+  </si>
+  <si>
+    <t>KeepBackups</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>How many backups of the report workbook to keep in Backups\ (0 = none).</t>
+  </si>
+  <si>
+    <t>FixFormulas</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Yes = save the report workbook in place (a backup is kept). No = save a copy in the output folder.</t>
-  </si>
-  <si>
-    <t>KeepBackups</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>How many backups of the report workbook to keep in Backups\ (0 = none).</t>
-  </si>
-  <si>
-    <t>FixFormulas</t>
-  </si>
-  <si>
     <t>Put back formulas that were typed over / broken (#REF!) in the Summary rows and the Core rows they use (Yes/No).</t>
   </si>
   <si>
@@ -203,13 +215,61 @@
     <t>Yellow cell right of each Performance % row uses the latest report day instead of always Friday (Yes/No).</t>
   </si>
   <si>
+    <t>CallInScan</t>
+  </si>
+  <si>
+    <t>Yes = the absent step asks whether to scan Outlook for call-in voicemail MP3s. No = never asks.</t>
+  </si>
+  <si>
     <t>OpenWhenDone</t>
   </si>
   <si>
-    <t>Open the output folder when done (Yes/No).</t>
-  </si>
-  <si>
-    <t>J:\Departments\Machine\4M\KACPER\DAILY OPS REPORTING</t>
+    <t>Open the workbook + the pictures folder when done (Yes/No).</t>
+  </si>
+  <si>
+    <t>StartShifts</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>Shifts that count for the start-time average (raw data).</t>
+  </si>
+  <si>
+    <t>StartEarlyMin</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Raw starts up to this many minutes BEFORE the shift start are looked at; negative = tracker time for that machine, else 0.</t>
+  </si>
+  <si>
+    <t>StartLateCap</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Raw first start later than this many minutes is not used (late logging / idle): tracker time if it has the machine, else left out.</t>
+  </si>
+  <si>
+    <t>OutlookSubject</t>
+  </si>
+  <si>
+    <t>Shift Hours and OT Report</t>
+  </si>
+  <si>
+    <t>Hours step also looks in Outlook (Inbox + its subfolders) for emails with this in the subject and takes their attachments. Blank = off.</t>
+  </si>
+  <si>
+    <t>PageFolder</t>
+  </si>
+  <si>
+    <t>J:\Departments\Machine\4M\KACPER\DAILY OPS REPORTING\Daily Ops Page</t>
+  </si>
+  <si>
+    <t>Folder on J: for the Daily Ops web page (index.html + the 2 pictures). Blank = off.</t>
   </si>
 </sst>
 </file>
@@ -596,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -608,9 +668,10 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,82 +699,94 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
       </c>
       <c r="E2">
         <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
       </c>
       <c r="E3">
         <v>154</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>145</v>
       </c>
       <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
       </c>
       <c r="E5">
         <v>175</v>
@@ -722,10 +795,13 @@
         <v>10177</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -745,169 +821,235 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
+      <c r="C17" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
